--- a/results/trace_ann29_temp06_4096_results.xlsx
+++ b/results/trace_ann29_temp06_4096_results.xlsx
@@ -930,7 +930,7 @@
         <v>82</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>1000</v>
@@ -1591,7 +1591,7 @@
         <v>67</v>
       </c>
       <c r="E31">
-        <v>35.64736305416392</v>
+        <v>36.26805270933633</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1602,7 +1602,7 @@
         <v>68</v>
       </c>
       <c r="E32">
-        <v>35.18908512300154</v>
+        <v>35.85410975354341</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1670,7 @@
         <v>82</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>1000</v>

--- a/results/trace_ann29_temp06_4096_results.xlsx
+++ b/results/trace_ann29_temp06_4096_results.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.38013698630137</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="F12" t="n">
         <v>1168</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17.38013698630137</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="I12" t="n">
         <v>1168</v>
